--- a/OUTPUT/direct_Q8Y7H7_Listeria_monocytogenes_EGD-e.xlsx
+++ b/OUTPUT/direct_Q8Y7H7_Listeria_monocytogenes_EGD-e.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6732</v>
+        <v>0.6731307477009196</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9054</v>
+        <v>0.9052379048380648</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8642</v>
+        <v>0.8640543782487006</v>
       </c>
     </row>
   </sheetData>
